--- a/data/nzd0036/nzd0036.xlsx
+++ b/data/nzd0036/nzd0036.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N589"/>
+  <dimension ref="A1:N596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28708,6 +28708,342 @@
         <v>347.84</v>
       </c>
       <c r="N589" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>367.18</v>
+      </c>
+      <c r="C590" t="n">
+        <v>358.43</v>
+      </c>
+      <c r="D590" t="n">
+        <v>350.7</v>
+      </c>
+      <c r="E590" t="n">
+        <v>354.32</v>
+      </c>
+      <c r="F590" t="n">
+        <v>356.92</v>
+      </c>
+      <c r="G590" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="H590" t="n">
+        <v>349.13</v>
+      </c>
+      <c r="I590" t="n">
+        <v>352.2</v>
+      </c>
+      <c r="J590" t="n">
+        <v>356.53</v>
+      </c>
+      <c r="K590" t="n">
+        <v>356.17</v>
+      </c>
+      <c r="L590" t="n">
+        <v>355.64</v>
+      </c>
+      <c r="M590" t="n">
+        <v>348.08</v>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>369.06</v>
+      </c>
+      <c r="C591" t="n">
+        <v>359.63</v>
+      </c>
+      <c r="D591" t="n">
+        <v>352.03</v>
+      </c>
+      <c r="E591" t="n">
+        <v>355.74</v>
+      </c>
+      <c r="F591" t="n">
+        <v>357.89</v>
+      </c>
+      <c r="G591" t="n">
+        <v>351.68</v>
+      </c>
+      <c r="H591" t="n">
+        <v>350.27</v>
+      </c>
+      <c r="I591" t="n">
+        <v>352.97</v>
+      </c>
+      <c r="J591" t="n">
+        <v>357.48</v>
+      </c>
+      <c r="K591" t="n">
+        <v>356.82</v>
+      </c>
+      <c r="L591" t="n">
+        <v>356.74</v>
+      </c>
+      <c r="M591" t="n">
+        <v>347.23</v>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>367.39</v>
+      </c>
+      <c r="C592" t="n">
+        <v>358.29</v>
+      </c>
+      <c r="D592" t="n">
+        <v>350.91</v>
+      </c>
+      <c r="E592" t="n">
+        <v>355.32</v>
+      </c>
+      <c r="F592" t="n">
+        <v>357.29</v>
+      </c>
+      <c r="G592" t="n">
+        <v>350.98</v>
+      </c>
+      <c r="H592" t="n">
+        <v>349.08</v>
+      </c>
+      <c r="I592" t="n">
+        <v>351.48</v>
+      </c>
+      <c r="J592" t="n">
+        <v>356.16</v>
+      </c>
+      <c r="K592" t="n">
+        <v>356.21</v>
+      </c>
+      <c r="L592" t="n">
+        <v>355.54</v>
+      </c>
+      <c r="M592" t="n">
+        <v>345.59</v>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>367.22</v>
+      </c>
+      <c r="C593" t="n">
+        <v>358.29</v>
+      </c>
+      <c r="D593" t="n">
+        <v>350.57</v>
+      </c>
+      <c r="E593" t="n">
+        <v>355.38</v>
+      </c>
+      <c r="F593" t="n">
+        <v>357.29</v>
+      </c>
+      <c r="G593" t="n">
+        <v>351.02</v>
+      </c>
+      <c r="H593" t="n">
+        <v>348.43</v>
+      </c>
+      <c r="I593" t="n">
+        <v>351.1</v>
+      </c>
+      <c r="J593" t="n">
+        <v>355.6</v>
+      </c>
+      <c r="K593" t="n">
+        <v>357.06</v>
+      </c>
+      <c r="L593" t="n">
+        <v>355.48</v>
+      </c>
+      <c r="M593" t="n">
+        <v>346.14</v>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>368.44</v>
+      </c>
+      <c r="C594" t="n">
+        <v>359.34</v>
+      </c>
+      <c r="D594" t="n">
+        <v>350.56</v>
+      </c>
+      <c r="E594" t="n">
+        <v>355.11</v>
+      </c>
+      <c r="F594" t="n">
+        <v>356.85</v>
+      </c>
+      <c r="G594" t="n">
+        <v>350.78</v>
+      </c>
+      <c r="H594" t="n">
+        <v>348.17</v>
+      </c>
+      <c r="I594" t="n">
+        <v>350.86</v>
+      </c>
+      <c r="J594" t="n">
+        <v>355.63</v>
+      </c>
+      <c r="K594" t="n">
+        <v>356.82</v>
+      </c>
+      <c r="L594" t="n">
+        <v>355.46</v>
+      </c>
+      <c r="M594" t="n">
+        <v>345.36</v>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>368.84</v>
+      </c>
+      <c r="C595" t="n">
+        <v>359.79</v>
+      </c>
+      <c r="D595" t="n">
+        <v>350.64</v>
+      </c>
+      <c r="E595" t="n">
+        <v>355.07</v>
+      </c>
+      <c r="F595" t="n">
+        <v>356.68</v>
+      </c>
+      <c r="G595" t="n">
+        <v>350.73</v>
+      </c>
+      <c r="H595" t="n">
+        <v>348.07</v>
+      </c>
+      <c r="I595" t="n">
+        <v>350.93</v>
+      </c>
+      <c r="J595" t="n">
+        <v>355.54</v>
+      </c>
+      <c r="K595" t="n">
+        <v>356.85</v>
+      </c>
+      <c r="L595" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="M595" t="n">
+        <v>344.2</v>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>369.84</v>
+      </c>
+      <c r="C596" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="D596" t="n">
+        <v>351.25</v>
+      </c>
+      <c r="E596" t="n">
+        <v>356.03</v>
+      </c>
+      <c r="F596" t="n">
+        <v>357.3</v>
+      </c>
+      <c r="G596" t="n">
+        <v>351.52</v>
+      </c>
+      <c r="H596" t="n">
+        <v>348.29</v>
+      </c>
+      <c r="I596" t="n">
+        <v>351.29</v>
+      </c>
+      <c r="J596" t="n">
+        <v>356.09</v>
+      </c>
+      <c r="K596" t="n">
+        <v>357.6</v>
+      </c>
+      <c r="L596" t="n">
+        <v>355.08</v>
+      </c>
+      <c r="M596" t="n">
+        <v>345.11</v>
+      </c>
+      <c r="N596" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28724,7 +29060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B598"/>
+  <dimension ref="A1:B605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34707,6 +35043,76 @@
       </c>
       <c r="B598" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>-0.57</v>
       </c>
     </row>
   </sheetData>
@@ -34875,28 +35281,28 @@
         <v>0.07480000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.253768370329597</v>
+        <v>0.2456022767817371</v>
       </c>
       <c r="J2" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="K2" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09830288795193631</v>
+        <v>0.09456898447589379</v>
       </c>
       <c r="M2" t="n">
-        <v>4.675040430105808</v>
+        <v>4.671833791088273</v>
       </c>
       <c r="N2" t="n">
-        <v>34.95581855443496</v>
+        <v>34.70137017096837</v>
       </c>
       <c r="O2" t="n">
-        <v>5.912344590298755</v>
+        <v>5.890786888945175</v>
       </c>
       <c r="P2" t="n">
-        <v>365.0303557216959</v>
+        <v>365.1134395757986</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34953,28 +35359,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4520449057653671</v>
+        <v>0.4434837378827949</v>
       </c>
       <c r="J3" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="K3" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3626740662077829</v>
+        <v>0.358278516772637</v>
       </c>
       <c r="M3" t="n">
-        <v>3.543173678484468</v>
+        <v>3.550261824939905</v>
       </c>
       <c r="N3" t="n">
-        <v>21.2499709793582</v>
+        <v>21.16685886157616</v>
       </c>
       <c r="O3" t="n">
-        <v>4.609769080914814</v>
+        <v>4.600745468027562</v>
       </c>
       <c r="P3" t="n">
-        <v>350.7221507171776</v>
+        <v>350.8092587282354</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35031,28 +35437,28 @@
         <v>0.1005</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4019891303563943</v>
+        <v>0.3904472421368954</v>
       </c>
       <c r="J4" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="K4" t="n">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09647814840082281</v>
+        <v>0.09351841848957432</v>
       </c>
       <c r="M4" t="n">
-        <v>7.773309015564382</v>
+        <v>7.745057859459671</v>
       </c>
       <c r="N4" t="n">
-        <v>89.10971352416362</v>
+        <v>88.35188345889462</v>
       </c>
       <c r="O4" t="n">
-        <v>9.439794146281137</v>
+        <v>9.399568259175238</v>
       </c>
       <c r="P4" t="n">
-        <v>345.1637752800405</v>
+        <v>345.2816905114456</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35109,28 +35515,28 @@
         <v>0.1076</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4027491816026472</v>
+        <v>0.3941897553128297</v>
       </c>
       <c r="J5" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="K5" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1109445801076812</v>
+        <v>0.1091796085699809</v>
       </c>
       <c r="M5" t="n">
-        <v>7.178228021144398</v>
+        <v>7.134442988408422</v>
       </c>
       <c r="N5" t="n">
-        <v>76.92051251716548</v>
+        <v>76.17886318279444</v>
       </c>
       <c r="O5" t="n">
-        <v>8.770433998221836</v>
+        <v>8.728050365505142</v>
       </c>
       <c r="P5" t="n">
-        <v>348.1869053332347</v>
+        <v>348.2740001552736</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35187,28 +35593,28 @@
         <v>0.0897</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3776259600128569</v>
+        <v>0.3656058423651353</v>
       </c>
       <c r="J6" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="K6" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1100227990033074</v>
+        <v>0.1059480081966743</v>
       </c>
       <c r="M6" t="n">
-        <v>6.579867758831471</v>
+        <v>6.55727291280464</v>
       </c>
       <c r="N6" t="n">
-        <v>68.26057930821884</v>
+        <v>67.77529821996806</v>
       </c>
       <c r="O6" t="n">
-        <v>8.261996084979636</v>
+        <v>8.232575430566554</v>
       </c>
       <c r="P6" t="n">
-        <v>352.2793242902925</v>
+        <v>352.401646187682</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35265,28 +35671,28 @@
         <v>0.0914</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3327952641192857</v>
+        <v>0.3214047776944549</v>
       </c>
       <c r="J7" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="K7" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09057386073448415</v>
+        <v>0.08678050652431868</v>
       </c>
       <c r="M7" t="n">
-        <v>6.431682724711288</v>
+        <v>6.412671486550908</v>
       </c>
       <c r="N7" t="n">
-        <v>65.80651933743418</v>
+        <v>65.3179962576141</v>
       </c>
       <c r="O7" t="n">
-        <v>8.112121753119474</v>
+        <v>8.081954977455275</v>
       </c>
       <c r="P7" t="n">
-        <v>347.0714232368428</v>
+        <v>347.1873331274286</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35343,28 +35749,28 @@
         <v>0.0832</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2672506584012065</v>
+        <v>0.2516642831026542</v>
       </c>
       <c r="J8" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="K8" t="n">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05939556867225859</v>
+        <v>0.05398711526055544</v>
       </c>
       <c r="M8" t="n">
-        <v>6.492006788680878</v>
+        <v>6.491130419626429</v>
       </c>
       <c r="N8" t="n">
-        <v>67.03536052203856</v>
+        <v>66.78415194994169</v>
       </c>
       <c r="O8" t="n">
-        <v>8.187512474618806</v>
+        <v>8.172157117306403</v>
       </c>
       <c r="P8" t="n">
-        <v>348.4257682364756</v>
+        <v>348.584310135989</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35421,28 +35827,28 @@
         <v>0.0833</v>
       </c>
       <c r="I9" t="n">
-        <v>0.219354433020855</v>
+        <v>0.2051032363388292</v>
       </c>
       <c r="J9" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="K9" t="n">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04965871368944996</v>
+        <v>0.04447832643488692</v>
       </c>
       <c r="M9" t="n">
-        <v>5.907788162731677</v>
+        <v>5.905571950321067</v>
       </c>
       <c r="N9" t="n">
-        <v>54.57457578907127</v>
+        <v>54.382660417223</v>
       </c>
       <c r="O9" t="n">
-        <v>7.387460713199852</v>
+        <v>7.374460008517437</v>
       </c>
       <c r="P9" t="n">
-        <v>351.9006321145264</v>
+        <v>352.0455940999978</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35499,28 +35905,28 @@
         <v>0.0867</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2352555332578399</v>
+        <v>0.2219545794686273</v>
       </c>
       <c r="J10" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="K10" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07397467940365743</v>
+        <v>0.06747660395315069</v>
       </c>
       <c r="M10" t="n">
-        <v>5.149455003132007</v>
+        <v>5.145816325912159</v>
       </c>
       <c r="N10" t="n">
-        <v>40.99865005105502</v>
+        <v>40.90815984701269</v>
       </c>
       <c r="O10" t="n">
-        <v>6.403018823262588</v>
+        <v>6.395948705783427</v>
       </c>
       <c r="P10" t="n">
-        <v>355.6521542535912</v>
+        <v>355.7875182219603</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35577,28 +35983,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1982063878872485</v>
+        <v>0.1875702991239046</v>
       </c>
       <c r="J11" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="K11" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05445371959518719</v>
+        <v>0.05002654480144786</v>
       </c>
       <c r="M11" t="n">
-        <v>5.05336550707371</v>
+        <v>5.044341130599452</v>
       </c>
       <c r="N11" t="n">
-        <v>40.36831545504405</v>
+        <v>40.1434143480488</v>
       </c>
       <c r="O11" t="n">
-        <v>6.353606491988944</v>
+        <v>6.335883075629537</v>
       </c>
       <c r="P11" t="n">
-        <v>356.1229894054662</v>
+        <v>356.2312151797486</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35655,28 +36061,28 @@
         <v>0.0506</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4288882815914176</v>
+        <v>0.4212597838980993</v>
       </c>
       <c r="J12" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="K12" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1800063325441351</v>
+        <v>0.1783209228381695</v>
       </c>
       <c r="M12" t="n">
-        <v>5.483341828004381</v>
+        <v>5.455019600549574</v>
       </c>
       <c r="N12" t="n">
-        <v>49.58623889566394</v>
+        <v>49.13320914187526</v>
       </c>
       <c r="O12" t="n">
-        <v>7.041749704133479</v>
+        <v>7.009508480762062</v>
       </c>
       <c r="P12" t="n">
-        <v>347.3800315154501</v>
+        <v>347.4576698148895</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35733,28 +36139,28 @@
         <v>0.0723</v>
       </c>
       <c r="I13" t="n">
-        <v>0.657151434213206</v>
+        <v>0.6310535799468705</v>
       </c>
       <c r="J13" t="n">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="K13" t="n">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2478355294727389</v>
+        <v>0.2344469644916195</v>
       </c>
       <c r="M13" t="n">
-        <v>6.801457304573135</v>
+        <v>6.84497937177464</v>
       </c>
       <c r="N13" t="n">
-        <v>76.40043100364095</v>
+        <v>76.97270023424933</v>
       </c>
       <c r="O13" t="n">
-        <v>8.740734008287916</v>
+        <v>8.773408700969615</v>
       </c>
       <c r="P13" t="n">
-        <v>339.5572973708047</v>
+        <v>339.8262684207202</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35792,7 +36198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N589"/>
+  <dimension ref="A1:N596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78175,6 +78581,510 @@
         </is>
       </c>
     </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>-34.9616453218878,173.67017320751506</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>-34.96166119538922,173.6710775946065</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>-34.96164677566938,173.67199051033697</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>-34.96140930595316,173.67285607760678</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>-34.96115355482751,173.67370424795317</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>-34.9608544588058,173.67453581580997</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>-34.960510345162135,173.67533462132707</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>-34.96010181585668,173.67609290108652</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>-34.95963518955543,173.67679729438294</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>-34.959098948461026,173.67743074016164</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>-34.95847954115227,173.67794680523716</t>
+        </is>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>-34.95781764133823,173.67835327768987</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>-34.96162843798438,173.67017136211663</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>-34.96165043261946,173.67107623872297</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>-34.961635024986066,173.67198759841418</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>-34.96139709561561,173.67285139563944</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>-34.961145539188244,173.6736999961742</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>-34.96084552497109,173.6745298640141</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>-34.96050146670808,173.67532832829255</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>-34.96009605259009,173.6760881978869</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>-34.95962876872482,173.6767904067271</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>-34.95909530023397,173.67742516817341</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>-34.95847498254557,173.67793610512047</t>
+        </is>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>-34.957820399158564,173.67836196383973</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>-34.96164343591987,173.67017300138008</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>-34.961662451045704,173.67107775279294</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>-34.96164492029833,173.67199005055963</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>-34.96140070712393,173.67285278044653</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>-34.961150497315636,173.67370262614048</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>-34.96085105920501,173.67453355096714</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>-34.96051073456801,173.6753348973374</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>-34.960107204885006,173.67609729888414</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>-34.95963769029986,173.6767999769439</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>-34.95909872395475,173.67743039727006</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>-34.95847995557102,173.67794777797508</t>
+        </is>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>-34.957825720127786,173.67837872300112</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>-34.96164496265581,173.67017316825124</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>-34.961662451045704,173.67107775279294</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>-34.961647924232395,173.67199079496106</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>-34.961400191194166,173.67285258261694</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>-34.961150497315636,173.67370262614048</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>-34.96085074296308,173.67453334028409</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>-34.96051579684426,173.67533848547177</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>-34.96011004909434,173.67609961994424</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>-34.959641475210255,173.6768040370365</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>-34.959093953196216,173.67742311082404</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>-34.95848020422227,173.67794836161787</t>
+        </is>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>-34.95782393565667,173.6783731025504</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>-34.96163400608021,173.67017197070538</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>-34.96165303362215,173.6710765663948</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>-34.961648012583396,173.6719908168552</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>-34.96140251287808,173.67285347285014</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>-34.96115413327569,173.6737045547826</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>-34.96085264041468,173.6745346043824</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>-34.96051782175474,173.67533992072566</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>-34.96011184543705,173.676101085877</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>-34.95964127244721,173.67680381953153</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>-34.95909530023397,173.67742516817341</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>-34.958480287106,173.67794855616543</t>
+        </is>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>-34.957826466361084,173.6783810733715</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>-34.96163041376031,173.67017157806748</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>-34.961648997583474,173.67107605793856</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>-34.96164730577539,173.67199064170194</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>-34.96140285683124,173.67285360473653</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>-34.96115553807842,173.67370529993985</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>-34.9608530357171,173.67453486773618</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>-34.960518600566466,173.67534047274637</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>-34.96011132150376,173.6761006583133</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>-34.959641880736356,173.67680447204646</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>-34.95909513185425,173.67742491100475</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>-34.95848136459469,173.67795108528415</t>
+        </is>
+      </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>-34.957830229971826,173.678392927414</t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>-34.9616214329606,173.67017059647284</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>-34.96164487185505,173.67107553818332</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>-34.961641916364265,173.67198930615828</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>-34.96139460195509,173.6728504394632</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>-34.961150414680176,173.6737025823077</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>-34.96084678993885,173.67453070674617</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>-34.96051688718068,173.6753392583008</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>-34.960108626989694,173.6760984594142</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>-34.95963816341367,173.67680048445544</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>-34.95909092236114,173.67741848178818</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>-34.95848186189714,173.67795225256972</t>
+        </is>
+      </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>-34.95782727748419,173.67838362812194</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0036/nzd0036.xlsx
+++ b/data/nzd0036/nzd0036.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N596"/>
+  <dimension ref="A1:N600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29044,6 +29044,198 @@
         <v>345.11</v>
       </c>
       <c r="N596" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>370.44</v>
+      </c>
+      <c r="C597" t="n">
+        <v>360.83</v>
+      </c>
+      <c r="D597" t="n">
+        <v>351.91</v>
+      </c>
+      <c r="E597" t="n">
+        <v>356.58</v>
+      </c>
+      <c r="F597" t="n">
+        <v>357.58</v>
+      </c>
+      <c r="G597" t="n">
+        <v>351.72</v>
+      </c>
+      <c r="H597" t="n">
+        <v>348.76</v>
+      </c>
+      <c r="I597" t="n">
+        <v>351.75</v>
+      </c>
+      <c r="J597" t="n">
+        <v>356.45</v>
+      </c>
+      <c r="K597" t="n">
+        <v>358.22</v>
+      </c>
+      <c r="L597" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="M597" t="n">
+        <v>345.57</v>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>371.07</v>
+      </c>
+      <c r="C598" t="n">
+        <v>361.43</v>
+      </c>
+      <c r="D598" t="n">
+        <v>352.21</v>
+      </c>
+      <c r="E598" t="n">
+        <v>356.97</v>
+      </c>
+      <c r="F598" t="n">
+        <v>358.07</v>
+      </c>
+      <c r="G598" t="n">
+        <v>352.12</v>
+      </c>
+      <c r="H598" t="n">
+        <v>349</v>
+      </c>
+      <c r="I598" t="n">
+        <v>352.08</v>
+      </c>
+      <c r="J598" t="n">
+        <v>356.78</v>
+      </c>
+      <c r="K598" t="n">
+        <v>358.75</v>
+      </c>
+      <c r="L598" t="n">
+        <v>356.77</v>
+      </c>
+      <c r="M598" t="n">
+        <v>345.22</v>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>371.39</v>
+      </c>
+      <c r="C599" t="n">
+        <v>361.68</v>
+      </c>
+      <c r="D599" t="n">
+        <v>351.89</v>
+      </c>
+      <c r="E599" t="n">
+        <v>356.82</v>
+      </c>
+      <c r="F599" t="n">
+        <v>357.95</v>
+      </c>
+      <c r="G599" t="n">
+        <v>352.05</v>
+      </c>
+      <c r="H599" t="n">
+        <v>348.84</v>
+      </c>
+      <c r="I599" t="n">
+        <v>352.06</v>
+      </c>
+      <c r="J599" t="n">
+        <v>356.68</v>
+      </c>
+      <c r="K599" t="n">
+        <v>358.82</v>
+      </c>
+      <c r="L599" t="n">
+        <v>356.91</v>
+      </c>
+      <c r="M599" t="n">
+        <v>345.32</v>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>371.58</v>
+      </c>
+      <c r="C600" t="n">
+        <v>361.91</v>
+      </c>
+      <c r="D600" t="n">
+        <v>352.23</v>
+      </c>
+      <c r="E600" t="n">
+        <v>357.12</v>
+      </c>
+      <c r="F600" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="G600" t="n">
+        <v>352.54</v>
+      </c>
+      <c r="H600" t="n">
+        <v>349.42</v>
+      </c>
+      <c r="I600" t="n">
+        <v>352.61</v>
+      </c>
+      <c r="J600" t="n">
+        <v>357.43</v>
+      </c>
+      <c r="K600" t="n">
+        <v>359.19</v>
+      </c>
+      <c r="L600" t="n">
+        <v>357.41</v>
+      </c>
+      <c r="M600" t="n">
+        <v>346.26</v>
+      </c>
+      <c r="N600" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29060,7 +29252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B605"/>
+  <dimension ref="A1:B609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35113,6 +35305,46 @@
       </c>
       <c r="B605" t="n">
         <v>-0.57</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -35281,28 +35513,28 @@
         <v>0.07480000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2456022767817371</v>
+        <v>0.2447917362046468</v>
       </c>
       <c r="J2" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="K2" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09456898447589379</v>
+        <v>0.09528840231477953</v>
       </c>
       <c r="M2" t="n">
-        <v>4.671833791088273</v>
+        <v>4.645726448247729</v>
       </c>
       <c r="N2" t="n">
-        <v>34.70137017096837</v>
+        <v>34.47348393438403</v>
       </c>
       <c r="O2" t="n">
-        <v>5.890786888945175</v>
+        <v>5.871412430955948</v>
       </c>
       <c r="P2" t="n">
-        <v>365.1134395757986</v>
+        <v>365.1217134519752</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35359,28 +35591,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4434837378827949</v>
+        <v>0.4417675868890816</v>
       </c>
       <c r="J3" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="K3" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="L3" t="n">
-        <v>0.358278516772637</v>
+        <v>0.3598282417855541</v>
       </c>
       <c r="M3" t="n">
-        <v>3.550261824939905</v>
+        <v>3.536304960288681</v>
       </c>
       <c r="N3" t="n">
-        <v>21.16685886157616</v>
+        <v>21.03829392638962</v>
       </c>
       <c r="O3" t="n">
-        <v>4.600745468027562</v>
+        <v>4.586752001840694</v>
       </c>
       <c r="P3" t="n">
-        <v>350.8092587282354</v>
+        <v>350.8267826274911</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35437,28 +35669,28 @@
         <v>0.1005</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3904472421368954</v>
+        <v>0.3855829508746886</v>
       </c>
       <c r="J4" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="K4" t="n">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09351841848957432</v>
+        <v>0.09258908778773212</v>
       </c>
       <c r="M4" t="n">
-        <v>7.745057859459671</v>
+        <v>7.719788218144133</v>
       </c>
       <c r="N4" t="n">
-        <v>88.35188345889462</v>
+        <v>87.85466639742091</v>
       </c>
       <c r="O4" t="n">
-        <v>9.399568259175238</v>
+        <v>9.373082011666222</v>
       </c>
       <c r="P4" t="n">
-        <v>345.2816905114456</v>
+        <v>345.3315663265295</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35515,28 +35747,28 @@
         <v>0.1076</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3941897553128297</v>
+        <v>0.3915487841493097</v>
       </c>
       <c r="J5" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="K5" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1091796085699809</v>
+        <v>0.1093042815036003</v>
       </c>
       <c r="M5" t="n">
-        <v>7.134442988408422</v>
+        <v>7.099256463315541</v>
       </c>
       <c r="N5" t="n">
-        <v>76.17886318279444</v>
+        <v>75.69819233255861</v>
       </c>
       <c r="O5" t="n">
-        <v>8.728050365505142</v>
+        <v>8.700470810971014</v>
       </c>
       <c r="P5" t="n">
-        <v>348.2740001552736</v>
+        <v>348.3009728035494</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35593,28 +35825,28 @@
         <v>0.0897</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3656058423651353</v>
+        <v>0.3600447991843005</v>
       </c>
       <c r="J6" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="K6" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1059480081966743</v>
+        <v>0.1043118387253444</v>
       </c>
       <c r="M6" t="n">
-        <v>6.55727291280464</v>
+        <v>6.53864363934057</v>
       </c>
       <c r="N6" t="n">
-        <v>67.77529821996806</v>
+        <v>67.4462604714202</v>
       </c>
       <c r="O6" t="n">
-        <v>8.232575430566554</v>
+        <v>8.21256722781739</v>
       </c>
       <c r="P6" t="n">
-        <v>352.401646187682</v>
+        <v>352.4584429646255</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35671,28 +35903,28 @@
         <v>0.0914</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3214047776944549</v>
+        <v>0.3165702849422322</v>
       </c>
       <c r="J7" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="K7" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08678050652431868</v>
+        <v>0.08546937854633074</v>
       </c>
       <c r="M7" t="n">
-        <v>6.412671486550908</v>
+        <v>6.393687792588822</v>
       </c>
       <c r="N7" t="n">
-        <v>65.3179962576141</v>
+        <v>64.9754892166676</v>
       </c>
       <c r="O7" t="n">
-        <v>8.081954977455275</v>
+        <v>8.060737510716224</v>
       </c>
       <c r="P7" t="n">
-        <v>347.1873331274286</v>
+        <v>347.2367083752437</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35749,28 +35981,28 @@
         <v>0.0832</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2516642831026542</v>
+        <v>0.2434851870809274</v>
       </c>
       <c r="J8" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="K8" t="n">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05398711526055544</v>
+        <v>0.05124527214656605</v>
       </c>
       <c r="M8" t="n">
-        <v>6.491130419626429</v>
+        <v>6.487652697446936</v>
       </c>
       <c r="N8" t="n">
-        <v>66.78415194994169</v>
+        <v>66.60492112174136</v>
       </c>
       <c r="O8" t="n">
-        <v>8.172157117306403</v>
+        <v>8.161183806393614</v>
       </c>
       <c r="P8" t="n">
-        <v>348.584310135989</v>
+        <v>348.6678040190926</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35827,28 +36059,28 @@
         <v>0.0833</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2051032363388292</v>
+        <v>0.1981044967156051</v>
       </c>
       <c r="J9" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="K9" t="n">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04447832643488692</v>
+        <v>0.04207843945017287</v>
       </c>
       <c r="M9" t="n">
-        <v>5.905571950321067</v>
+        <v>5.899244078969475</v>
       </c>
       <c r="N9" t="n">
-        <v>54.382660417223</v>
+        <v>54.2150758010001</v>
       </c>
       <c r="O9" t="n">
-        <v>7.374460008517437</v>
+        <v>7.363088740535462</v>
       </c>
       <c r="P9" t="n">
-        <v>352.0455940999978</v>
+        <v>352.1170373442524</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35905,28 +36137,28 @@
         <v>0.0867</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2219545794686273</v>
+        <v>0.2156098111976322</v>
       </c>
       <c r="J10" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="K10" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06747660395315069</v>
+        <v>0.0645865417559538</v>
       </c>
       <c r="M10" t="n">
-        <v>5.145816325912159</v>
+        <v>5.139041995608962</v>
       </c>
       <c r="N10" t="n">
-        <v>40.90815984701269</v>
+        <v>40.79624392438858</v>
       </c>
       <c r="O10" t="n">
-        <v>6.395948705783427</v>
+        <v>6.387193744077956</v>
       </c>
       <c r="P10" t="n">
-        <v>355.7875182219603</v>
+        <v>355.852318369415</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35983,28 +36215,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1875702991239046</v>
+        <v>0.1842940516639848</v>
       </c>
       <c r="J11" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="K11" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05002654480144786</v>
+        <v>0.04902683823816179</v>
       </c>
       <c r="M11" t="n">
-        <v>5.044341130599452</v>
+        <v>5.026315457620123</v>
       </c>
       <c r="N11" t="n">
-        <v>40.1434143480488</v>
+        <v>39.9189002924719</v>
       </c>
       <c r="O11" t="n">
-        <v>6.335883075629537</v>
+        <v>6.318140572389308</v>
       </c>
       <c r="P11" t="n">
-        <v>356.2312151797486</v>
+        <v>356.2646741503871</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36061,28 +36293,28 @@
         <v>0.0506</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4212597838980993</v>
+        <v>0.4186520994384975</v>
       </c>
       <c r="J12" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="K12" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1783209228381695</v>
+        <v>0.1786283376247884</v>
       </c>
       <c r="M12" t="n">
-        <v>5.455019600549574</v>
+        <v>5.430841240544758</v>
       </c>
       <c r="N12" t="n">
-        <v>49.13320914187526</v>
+        <v>48.83345636512617</v>
       </c>
       <c r="O12" t="n">
-        <v>7.009508480762062</v>
+        <v>6.988093900708988</v>
       </c>
       <c r="P12" t="n">
-        <v>347.4576698148895</v>
+        <v>347.4842993087096</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36139,28 +36371,28 @@
         <v>0.0723</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6310535799468705</v>
+        <v>0.6163791991546159</v>
       </c>
       <c r="J13" t="n">
+        <v>599</v>
+      </c>
+      <c r="K13" t="n">
         <v>595</v>
       </c>
-      <c r="K13" t="n">
-        <v>591</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.2344469644916195</v>
+        <v>0.2268488607875765</v>
       </c>
       <c r="M13" t="n">
-        <v>6.84497937177464</v>
+        <v>6.87108697104911</v>
       </c>
       <c r="N13" t="n">
-        <v>76.97270023424933</v>
+        <v>77.29670886843007</v>
       </c>
       <c r="O13" t="n">
-        <v>8.773408700969615</v>
+        <v>8.791854688769035</v>
       </c>
       <c r="P13" t="n">
-        <v>339.8262684207202</v>
+        <v>339.9780364233441</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36198,7 +36430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N596"/>
+  <dimension ref="A1:N600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79085,6 +79317,294 @@
         </is>
       </c>
     </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>-34.961616044480756,173.6701700075162</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>-34.961639669849646,173.67107488283986</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>-34.96163608519811,173.671987861144</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>-34.961389872598915,173.6728486260256</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>-34.96114810088741,173.67370135499007</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>-34.960845208729154,173.6745296533311</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>-34.96051322676556,173.67533666380348</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>-34.9601051839994,173.67609564970996</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>-34.95963573025692,173.6767978743961</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>-34.95908744251325,173.6774131669697</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>-34.95847730329091,173.67794155245247</t>
+        </is>
+      </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>-34.95782578501765,173.67837892738115</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>-34.96161038657691,173.67016938911178</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>-34.961634288464715,173.67107420489845</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>-34.961633434668016,173.67198720431944</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>-34.96138651905544,173.67284734013364</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>-34.96114405175002,173.6736992071844</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>-34.96084204630971,173.67452754650103</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>-34.9605113576174,173.67533533895391</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>-34.96010271402809,173.67609363405273</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>-34.959633499863195,173.6767954818418</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>-34.95908446780438,173.6774086236574</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>-34.958474858219915,173.67793581329914</t>
+        </is>
+      </c>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>-34.95782692059003,173.67838250403173</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>-34.96160751272099,173.67016907500164</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>-34.96163204622099,173.67107392242286</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>-34.961636261900104,173.6719879049323</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>-34.96138780887985,173.67284783470745</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>-34.961145043375495,173.6736997331776</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>-34.96084259973311,173.67452791519628</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>-34.960512603716175,173.67533622218696</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>-34.960102863723314,173.6760937562138</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>-34.95963417574009,173.67679620685826</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>-34.95908407491829,173.67740802359734</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>-34.95847427803354,173.67793445146617</t>
+        </is>
+      </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>-34.95782659614079,173.67838148213156</t>
+        </is>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>-34.961605806369036,173.67016888849875</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>-34.96162998335678,173.67107366254538</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>-34.96163325796602,173.67198716053113</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>-34.961385229231006,173.67284684555983</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>-34.96114297748906,173.67369863735843</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>-34.96083872576924,173.67452533432964</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>-34.96050808660806,173.6753330204673</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>-34.96009874710437,173.67609039678533</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>-34.959629106663286,173.67679076923525</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>-34.9590819982346,173.6774048518513</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>-34.95847220593918,173.67792958777727</t>
+        </is>
+      </c>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>-34.95782354631747,173.6783718762703</t>
+        </is>
+      </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0036/nzd0036.xlsx
+++ b/data/nzd0036/nzd0036.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N600"/>
+  <dimension ref="A1:N602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29236,6 +29236,102 @@
         <v>346.26</v>
       </c>
       <c r="N600" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>373.22</v>
+      </c>
+      <c r="C601" t="n">
+        <v>362.29</v>
+      </c>
+      <c r="D601" t="n">
+        <v>352.38</v>
+      </c>
+      <c r="E601" t="n">
+        <v>357.16</v>
+      </c>
+      <c r="F601" t="n">
+        <v>358.21</v>
+      </c>
+      <c r="G601" t="n">
+        <v>352.76</v>
+      </c>
+      <c r="H601" t="n">
+        <v>349.63</v>
+      </c>
+      <c r="I601" t="n">
+        <v>352.78</v>
+      </c>
+      <c r="J601" t="n">
+        <v>357.8</v>
+      </c>
+      <c r="K601" t="n">
+        <v>359.29</v>
+      </c>
+      <c r="L601" t="n">
+        <v>357.26</v>
+      </c>
+      <c r="M601" t="n">
+        <v>346.09</v>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>373.22</v>
+      </c>
+      <c r="C602" t="n">
+        <v>362.21</v>
+      </c>
+      <c r="D602" t="n">
+        <v>352.64</v>
+      </c>
+      <c r="E602" t="n">
+        <v>357.11</v>
+      </c>
+      <c r="F602" t="n">
+        <v>358.05</v>
+      </c>
+      <c r="G602" t="n">
+        <v>352.84</v>
+      </c>
+      <c r="H602" t="n">
+        <v>349.88</v>
+      </c>
+      <c r="I602" t="n">
+        <v>353.14</v>
+      </c>
+      <c r="J602" t="n">
+        <v>357.94</v>
+      </c>
+      <c r="K602" t="n">
+        <v>359.29</v>
+      </c>
+      <c r="L602" t="n">
+        <v>357.26</v>
+      </c>
+      <c r="M602" t="n">
+        <v>346.09</v>
+      </c>
+      <c r="N602" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29252,7 +29348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B609"/>
+  <dimension ref="A1:B611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35345,6 +35441,26 @@
       </c>
       <c r="B609" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -35513,28 +35629,28 @@
         <v>0.07480000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2447917362046468</v>
+        <v>0.2457224200069671</v>
       </c>
       <c r="J2" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K2" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09528840231477953</v>
+        <v>0.09657698923113089</v>
       </c>
       <c r="M2" t="n">
-        <v>4.645726448247729</v>
+        <v>4.634094573381442</v>
       </c>
       <c r="N2" t="n">
-        <v>34.47348393438403</v>
+        <v>34.36578972286819</v>
       </c>
       <c r="O2" t="n">
-        <v>5.871412430955948</v>
+        <v>5.862234192086511</v>
       </c>
       <c r="P2" t="n">
-        <v>365.1217134519752</v>
+        <v>365.1121805107594</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35591,28 +35707,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4417675868890816</v>
+        <v>0.4414144845644009</v>
       </c>
       <c r="J3" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K3" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3598282417855541</v>
+        <v>0.3611711275020064</v>
       </c>
       <c r="M3" t="n">
-        <v>3.536304960288681</v>
+        <v>3.526529985502712</v>
       </c>
       <c r="N3" t="n">
-        <v>21.03829392638962</v>
+        <v>20.9693006329534</v>
       </c>
       <c r="O3" t="n">
-        <v>4.586752001840694</v>
+        <v>4.579224894341115</v>
       </c>
       <c r="P3" t="n">
-        <v>350.8267826274911</v>
+        <v>350.8303994515722</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35669,28 +35785,28 @@
         <v>0.1005</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3855829508746886</v>
+        <v>0.3834852421393259</v>
       </c>
       <c r="J4" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K4" t="n">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09258908778773212</v>
+        <v>0.09226806926493847</v>
       </c>
       <c r="M4" t="n">
-        <v>7.719788218144133</v>
+        <v>7.705400508394411</v>
       </c>
       <c r="N4" t="n">
-        <v>87.85466639742091</v>
+        <v>87.59731479732562</v>
       </c>
       <c r="O4" t="n">
-        <v>9.373082011666222</v>
+        <v>9.359343716165446</v>
       </c>
       <c r="P4" t="n">
-        <v>345.3315663265295</v>
+        <v>345.3531365374398</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35747,28 +35863,28 @@
         <v>0.1076</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3915487841493097</v>
+        <v>0.3904125071822951</v>
       </c>
       <c r="J5" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K5" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1093042815036003</v>
+        <v>0.109452492572592</v>
       </c>
       <c r="M5" t="n">
-        <v>7.099256463315541</v>
+        <v>7.080940033566532</v>
       </c>
       <c r="N5" t="n">
-        <v>75.69819233255861</v>
+        <v>75.45676036428496</v>
       </c>
       <c r="O5" t="n">
-        <v>8.700470810971014</v>
+        <v>8.686585080702597</v>
       </c>
       <c r="P5" t="n">
-        <v>348.3009728035494</v>
+        <v>348.3126116340741</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35825,28 +35941,28 @@
         <v>0.0897</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3600447991843005</v>
+        <v>0.3574378019265441</v>
       </c>
       <c r="J6" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K6" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1043118387253444</v>
+        <v>0.1035777458772562</v>
       </c>
       <c r="M6" t="n">
-        <v>6.53864363934057</v>
+        <v>6.528643690506206</v>
       </c>
       <c r="N6" t="n">
-        <v>67.4462604714202</v>
+        <v>67.27696796778287</v>
       </c>
       <c r="O6" t="n">
-        <v>8.21256722781739</v>
+        <v>8.202253834634897</v>
       </c>
       <c r="P6" t="n">
-        <v>352.4584429646255</v>
+        <v>352.4851463222947</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35903,28 +36019,28 @@
         <v>0.0914</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3165702849422322</v>
+        <v>0.3146466845707455</v>
       </c>
       <c r="J7" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K7" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08546937854633074</v>
+        <v>0.08506531277854679</v>
       </c>
       <c r="M7" t="n">
-        <v>6.393687792588822</v>
+        <v>6.38189139019401</v>
       </c>
       <c r="N7" t="n">
-        <v>64.9754892166676</v>
+        <v>64.78928459982808</v>
       </c>
       <c r="O7" t="n">
-        <v>8.060737510716224</v>
+        <v>8.049179125838117</v>
       </c>
       <c r="P7" t="n">
-        <v>347.2367083752437</v>
+        <v>347.2564116904701</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35981,28 +36097,28 @@
         <v>0.0832</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2434851870809274</v>
+        <v>0.2399737307600345</v>
       </c>
       <c r="J8" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K8" t="n">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05124527214656605</v>
+        <v>0.05013401483492796</v>
       </c>
       <c r="M8" t="n">
-        <v>6.487652697446936</v>
+        <v>6.483129165825502</v>
       </c>
       <c r="N8" t="n">
-        <v>66.60492112174136</v>
+        <v>66.48317915201829</v>
       </c>
       <c r="O8" t="n">
-        <v>8.161183806393614</v>
+        <v>8.153721797560811</v>
       </c>
       <c r="P8" t="n">
-        <v>348.6678040190926</v>
+        <v>348.7037535329863</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36059,28 +36175,28 @@
         <v>0.0833</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1981044967156051</v>
+        <v>0.1952202118121958</v>
       </c>
       <c r="J9" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K9" t="n">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04207843945017287</v>
+        <v>0.04115644381954098</v>
       </c>
       <c r="M9" t="n">
-        <v>5.899244078969475</v>
+        <v>5.89325123878094</v>
       </c>
       <c r="N9" t="n">
-        <v>54.2150758010001</v>
+        <v>54.10208381105176</v>
       </c>
       <c r="O9" t="n">
-        <v>7.363088740535462</v>
+        <v>7.355411872291841</v>
       </c>
       <c r="P9" t="n">
-        <v>352.1170373442524</v>
+        <v>352.1465659855879</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36137,28 +36253,28 @@
         <v>0.0867</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2156098111976322</v>
+        <v>0.213169784955548</v>
       </c>
       <c r="J10" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K10" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0645865417559538</v>
+        <v>0.06359816481426894</v>
       </c>
       <c r="M10" t="n">
-        <v>5.139041995608962</v>
+        <v>5.132642046920242</v>
       </c>
       <c r="N10" t="n">
-        <v>40.79624392438858</v>
+        <v>40.70879444584803</v>
       </c>
       <c r="O10" t="n">
-        <v>6.387193744077956</v>
+        <v>6.380344383013195</v>
       </c>
       <c r="P10" t="n">
-        <v>355.852318369415</v>
+        <v>355.8773113924005</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36215,28 +36331,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1842940516639848</v>
+        <v>0.1830394422376495</v>
       </c>
       <c r="J11" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K11" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04902683823816179</v>
+        <v>0.04872421083602407</v>
       </c>
       <c r="M11" t="n">
-        <v>5.026315457620123</v>
+        <v>5.0155283661854</v>
       </c>
       <c r="N11" t="n">
-        <v>39.9189002924719</v>
+        <v>39.79882700047436</v>
       </c>
       <c r="O11" t="n">
-        <v>6.318140572389308</v>
+        <v>6.308631151087719</v>
       </c>
       <c r="P11" t="n">
-        <v>356.2646741503871</v>
+        <v>356.2775250436083</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36293,28 +36409,28 @@
         <v>0.0506</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4186520994384975</v>
+        <v>0.4176471039833781</v>
       </c>
       <c r="J12" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K12" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1786283376247884</v>
+        <v>0.1789950712010531</v>
       </c>
       <c r="M12" t="n">
-        <v>5.430841240544758</v>
+        <v>5.417487817989844</v>
       </c>
       <c r="N12" t="n">
-        <v>48.83345636512617</v>
+        <v>48.67914205050061</v>
       </c>
       <c r="O12" t="n">
-        <v>6.988093900708988</v>
+        <v>6.977043933536653</v>
       </c>
       <c r="P12" t="n">
-        <v>347.4842993087096</v>
+        <v>347.4945934203212</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36371,28 +36487,28 @@
         <v>0.0723</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6163791991546159</v>
+        <v>0.6095356393761981</v>
       </c>
       <c r="J13" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K13" t="n">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2268488607875765</v>
+        <v>0.2234235810032552</v>
       </c>
       <c r="M13" t="n">
-        <v>6.87108697104911</v>
+        <v>6.882770925258141</v>
       </c>
       <c r="N13" t="n">
-        <v>77.29670886843007</v>
+        <v>77.40995484987327</v>
       </c>
       <c r="O13" t="n">
-        <v>8.791854688769035</v>
+        <v>8.798292723584121</v>
       </c>
       <c r="P13" t="n">
-        <v>339.9780364233441</v>
+        <v>340.0490171289532</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36430,7 +36546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N600"/>
+  <dimension ref="A1:N602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79605,6 +79721,150 @@
         </is>
       </c>
     </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>-34.96159107785737,173.67016727868472</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>-34.96162657514631,173.67107323318257</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>-34.96163193270099,173.67198683211882</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>-34.961384885277816,173.6728467136735</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>-34.96114289485361,173.67369859352564</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>-34.960836986438515,173.67452417557328</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>-34.96050645110338,173.67533186122404</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>-34.96009747469484,173.67608935841662</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>-34.95962660591862,173.67678808667483</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>-34.959081436968745,173.67740399462264</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>-34.95847282756751,173.6779310468839</t>
+        </is>
+      </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>-34.95782409788133,173.67837361350047</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>-34.96159107785737,173.67016727868472</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>-34.96162729266431,173.67107332357472</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>-34.961629635574894,173.67198626287092</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>-34.9613853152193,173.67284687853143</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>-34.96114421702092,173.6736992948499</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>-34.960836353954605,173.67452375420734</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>-34.960504504073974,173.67533048117264</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>-34.96009478018055,173.67608715951826</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>-34.95962565969091,173.67678707165203</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>-34.959081436968745,173.67740399462264</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>-34.95847282756751,173.6779310468839</t>
+        </is>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>-34.95782409788133,173.67837361350047</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
